--- a/research/traditional_assets/database/data/egypt/egypt_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_brokerage_investment_banking.xlsx
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.177</v>
+        <v>-0.03015</v>
       </c>
       <c r="E2">
-        <v>0.677</v>
-      </c>
-      <c r="F2">
-        <v>0.14</v>
+        <v>-0.0397</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>90.616</v>
+        <v>51.877</v>
       </c>
       <c r="L2">
-        <v>0.2236261512492226</v>
+        <v>0.1409609155924613</v>
       </c>
       <c r="M2">
-        <v>7.067</v>
+        <v>17.393</v>
       </c>
       <c r="N2">
-        <v>0.007287520366283746</v>
+        <v>0.01861984282381858</v>
       </c>
       <c r="O2">
-        <v>0.07798843471351638</v>
+        <v>0.3352738207683559</v>
       </c>
       <c r="P2">
-        <v>7.067</v>
+        <v>17.393</v>
       </c>
       <c r="Q2">
-        <v>0.007287520366283746</v>
+        <v>0.01861984282381858</v>
       </c>
       <c r="R2">
-        <v>0.07798843471351638</v>
+        <v>0.3352738207683559</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,61 +636,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>731.807</v>
+        <v>1439.072</v>
       </c>
       <c r="V2">
-        <v>0.7546424814898839</v>
+        <v>1.540579224524709</v>
       </c>
       <c r="W2">
-        <v>-0.04447852760736196</v>
+        <v>-0.02491349480968858</v>
       </c>
       <c r="X2">
-        <v>0.05924370699295058</v>
+        <v>0.1125791895416486</v>
       </c>
       <c r="Y2">
-        <v>-0.1037222346003125</v>
+        <v>-0.1374926843513371</v>
       </c>
       <c r="Z2">
-        <v>0.4151987761630498</v>
+        <v>0.168201404390136</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05919662985981401</v>
+        <v>0.1115167855104068</v>
       </c>
       <c r="AC2">
-        <v>-0.05919662985981401</v>
+        <v>-0.1115167855104068</v>
       </c>
       <c r="AD2">
-        <v>1350.373</v>
+        <v>956.003</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1350.373</v>
+        <v>956.003</v>
       </c>
       <c r="AG2">
-        <v>618.566</v>
+        <v>-483.0690000000001</v>
       </c>
       <c r="AH2">
-        <v>0.5820289787609483</v>
+        <v>0.5057911850819581</v>
       </c>
       <c r="AI2">
-        <v>0.5698872863301969</v>
+        <v>0.4802895996527456</v>
       </c>
       <c r="AJ2">
-        <v>0.3894501437380454</v>
+        <v>-1.071006691172884</v>
       </c>
       <c r="AK2">
-        <v>0.3776955640618732</v>
+        <v>-0.8760772578890099</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.139</v>
+        <v>-2.202</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -707,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>El Kahera El Watania Investment (CASE:KWIN)</t>
+          <t>Osool ESB Securities Brokerage (CASE:EBSC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0761</v>
+        <v>-0.0471</v>
       </c>
       <c r="E3">
-        <v>0.677</v>
+        <v>0.0322</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,10 +731,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1.92</v>
+        <v>0.147</v>
       </c>
       <c r="L3">
-        <v>0.64</v>
+        <v>0.1906614785992218</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.011</v>
+        <v>2.71</v>
       </c>
       <c r="V3">
-        <v>0.001286549707602339</v>
+        <v>0.4927272727272727</v>
       </c>
       <c r="W3">
-        <v>0.3428571428571429</v>
+        <v>0.04468085106382978</v>
       </c>
       <c r="X3">
-        <v>0.05797766422549892</v>
+        <v>0.1091190460079253</v>
       </c>
       <c r="Y3">
-        <v>0.2848794786316439</v>
+        <v>-0.06443819494409547</v>
       </c>
       <c r="Z3">
-        <v>0.5425935973955507</v>
+        <v>0.2930444697833524</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05797766422549892</v>
+        <v>0.1091190460079253</v>
       </c>
       <c r="AC3">
-        <v>-0.05797766422549892</v>
+        <v>-0.1091190460079253</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -797,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.011</v>
+        <v>-2.71</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -806,16 +803,16 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.001288207050005855</v>
+        <v>-0.9713261648745519</v>
       </c>
       <c r="AK3">
-        <v>-0.001525870439728118</v>
+        <v>-15.05555555555554</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.008</v>
+        <v>-0.116</v>
       </c>
       <c r="AQ3">
         <v>-0</v>
@@ -837,26 +834,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.15</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
       <c r="K4">
-        <v>-0.126</v>
-      </c>
-      <c r="L4">
-        <v>-6.3</v>
+        <v>-0.391</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -880,31 +859,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.907</v>
+        <v>0.008</v>
       </c>
       <c r="V4">
-        <v>0.3160278745644599</v>
+        <v>0.004232804232804233</v>
       </c>
       <c r="W4">
-        <v>-0.1145454545454545</v>
+        <v>-0.3969543147208122</v>
       </c>
       <c r="X4">
-        <v>0.05797766422549892</v>
+        <v>0.1091190460079253</v>
       </c>
       <c r="Y4">
-        <v>-0.1725231187709534</v>
+        <v>-0.5060733607287374</v>
       </c>
       <c r="Z4">
-        <v>0.01841620626151013</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05797766422549892</v>
+        <v>0.1091190460079253</v>
       </c>
       <c r="AC4">
-        <v>-0.05797766422549892</v>
+        <v>-0.1091190460079253</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -916,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-0.907</v>
+        <v>-0.008</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -925,16 +904,16 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.4620478858889455</v>
+        <v>-0.004250797024442084</v>
       </c>
       <c r="AK4">
-        <v>-13.95384615384617</v>
+        <v>-0.01891252955082742</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.034</v>
+        <v>-0.015</v>
       </c>
       <c r="AQ4">
         <v>-0</v>
@@ -948,7 +927,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grand Capital for Financial Investments (CASE:GRCA)</t>
+          <t>El Kahera El Watania Investment (CASE:KWIN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,7 +936,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0444</v>
+        <v>-0.112</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-0.155</v>
+        <v>-0.239</v>
       </c>
       <c r="L5">
-        <v>-0.4068241469816273</v>
+        <v>-0.2918192918192918</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -999,61 +978,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.429</v>
+        <v>0.055</v>
       </c>
       <c r="V5">
-        <v>0.06422155688622755</v>
+        <v>0.01264367816091954</v>
       </c>
       <c r="W5">
-        <v>-0.05115511551155116</v>
+        <v>-0.03494152046783626</v>
       </c>
       <c r="X5">
-        <v>0.05824629150810927</v>
+        <v>0.1093194957022927</v>
       </c>
       <c r="Y5">
-        <v>-0.1094014070196604</v>
+        <v>-0.1442610161701289</v>
       </c>
       <c r="Z5">
-        <v>0.181169757489301</v>
+        <v>0.1329329654276903</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05826293817479728</v>
+        <v>0.1092770199398229</v>
       </c>
       <c r="AC5">
-        <v>-0.05826293817479728</v>
+        <v>-0.1092770199398229</v>
       </c>
       <c r="AD5">
-        <v>0.054</v>
+        <v>0.016</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.054</v>
+        <v>0.016</v>
       </c>
       <c r="AG5">
-        <v>-0.375</v>
+        <v>-0.039</v>
       </c>
       <c r="AH5">
-        <v>0.008019008019008018</v>
+        <v>0.003664681630783326</v>
       </c>
       <c r="AI5">
-        <v>0.01750972762645914</v>
+        <v>0.003061615001913509</v>
       </c>
       <c r="AJ5">
-        <v>-0.05947660586835845</v>
+        <v>-0.009046624913013222</v>
       </c>
       <c r="AK5">
-        <v>-0.1412429378531073</v>
+        <v>-0.007542061496809128</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.075</v>
+        <v>-0.005</v>
       </c>
       <c r="AQ5">
         <v>-0</v>
@@ -1067,7 +1046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Egyptian Arabian Company (Themar) for securities Brokerage EAC (CASE:EASB)</t>
+          <t>Grand Capital for Financial Investments (CASE:GRCA)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,10 +1055,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.177</v>
-      </c>
-      <c r="E6">
-        <v>0.243</v>
+        <v>0.195</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,91 +1070,91 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0.531</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="L6">
-        <v>0.2349557522123894</v>
+        <v>-0.05106382978723404</v>
       </c>
       <c r="M6">
-        <v>0.398</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.03431034482758621</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.7495291902071564</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0.398</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.03431034482758621</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.7495291902071564</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>3.76</v>
+        <v>0.32</v>
       </c>
       <c r="V6">
-        <v>0.3241379310344827</v>
+        <v>0.1167883211678832</v>
       </c>
       <c r="W6">
-        <v>0.1314356435643564</v>
+        <v>-0.02491349480968858</v>
       </c>
       <c r="X6">
-        <v>0.05832428948090806</v>
+        <v>0.1115455663729068</v>
       </c>
       <c r="Y6">
-        <v>0.07311135408344838</v>
+        <v>-0.1364590611825953</v>
       </c>
       <c r="Z6">
-        <v>0.802271920482783</v>
+        <v>0.6688804554079696</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05832053893806285</v>
+        <v>0.1109565969070591</v>
       </c>
       <c r="AC6">
-        <v>-0.05832053893806285</v>
+        <v>-0.1109565969070591</v>
       </c>
       <c r="AD6">
-        <v>0.121</v>
+        <v>0.122</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.121</v>
+        <v>0.122</v>
       </c>
       <c r="AG6">
-        <v>-3.639</v>
+        <v>-0.198</v>
       </c>
       <c r="AH6">
-        <v>0.01032335124989335</v>
+        <v>0.04262753319357093</v>
       </c>
       <c r="AI6">
-        <v>0.02749375142013179</v>
+        <v>0.05121746431570109</v>
       </c>
       <c r="AJ6">
-        <v>-0.4571033789724909</v>
+        <v>-0.07789142407553107</v>
       </c>
       <c r="AK6">
-        <v>-5.677067082683303</v>
+        <v>-0.09602327837051408</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>-0.168</v>
+      </c>
+      <c r="AQ6">
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -1189,7 +1165,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Osool ESB Securities Brokerage (CASE:EBSC)</t>
+          <t>Egyptian Arabian Company (Themar) for securities Brokerage EAC (CASE:EASB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1198,7 +1174,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0517</v>
+        <v>-0.0132</v>
+      </c>
+      <c r="E7">
+        <v>-0.0397</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1213,91 +1192,91 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-0.145</v>
+        <v>0.437</v>
       </c>
       <c r="L7">
-        <v>-0.142156862745098</v>
+        <v>0.3143884892086331</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>0.538</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.06099773242630386</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.231121281464531</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>0.538</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.06099773242630386</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.231121281464531</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="V7">
-        <v>0.09256198347107439</v>
+        <v>0.1360544217687075</v>
       </c>
       <c r="W7">
-        <v>-0.04447852760736196</v>
+        <v>0.1021028037383177</v>
       </c>
       <c r="X7">
-        <v>0.05924370699295058</v>
+        <v>0.1125791895416486</v>
       </c>
       <c r="Y7">
-        <v>-0.1037222346003125</v>
+        <v>-0.01047638580333081</v>
       </c>
       <c r="Z7">
-        <v>0.4033214709371293</v>
+        <v>2.168486739469579</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05919662985981401</v>
+        <v>0.1115167855104068</v>
       </c>
       <c r="AC7">
-        <v>-0.05919662985981401</v>
+        <v>-0.1115167855104068</v>
       </c>
       <c r="AD7">
-        <v>0.461</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.461</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG7">
-        <v>-0.659</v>
+        <v>-0.6399999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.03670089960990367</v>
+        <v>0.05970149253731343</v>
       </c>
       <c r="AI7">
-        <v>0.1229005598507065</v>
+        <v>0.1296296296296296</v>
       </c>
       <c r="AJ7">
-        <v>-0.05759986015208462</v>
+        <v>-0.07823960880195598</v>
       </c>
       <c r="AK7">
-        <v>-0.250475104522995</v>
+        <v>-0.2051282051282051</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.022</v>
-      </c>
-      <c r="AQ7">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1317,7 +1296,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.384</v>
+        <v>0.183</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1332,10 +1311,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0.041</v>
+        <v>-0.125</v>
       </c>
       <c r="L8">
-        <v>0.09512761020881672</v>
+        <v>-0.5841121495327103</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1344,7 +1323,7 @@
         <v>-0</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <v>-0</v>
@@ -1353,61 +1332,61 @@
         <v>-0</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.06</v>
+        <v>0.279</v>
       </c>
       <c r="V8">
-        <v>0.03658536585365853</v>
+        <v>0.344019728729963</v>
       </c>
       <c r="W8">
-        <v>0.05848787446504993</v>
+        <v>-0.1623376623376623</v>
       </c>
       <c r="X8">
-        <v>0.06480606297799567</v>
+        <v>0.122894555791537</v>
       </c>
       <c r="Y8">
-        <v>-0.006318188512945737</v>
+        <v>-0.2852322181291994</v>
       </c>
       <c r="Z8">
-        <v>1.422442244224423</v>
+        <v>0.2491268917345751</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.0640417411005981</v>
+        <v>0.1172226267329705</v>
       </c>
       <c r="AC8">
-        <v>-0.0640417411005981</v>
+        <v>-0.1172226267329705</v>
       </c>
       <c r="AD8">
-        <v>0.337</v>
+        <v>0.205</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.337</v>
+        <v>0.205</v>
       </c>
       <c r="AG8">
-        <v>0.277</v>
+        <v>-0.07400000000000004</v>
       </c>
       <c r="AH8">
-        <v>0.1704602933737987</v>
+        <v>0.2017716535433071</v>
       </c>
       <c r="AI8">
-        <v>0.3019713261648745</v>
+        <v>0.2835408022130014</v>
       </c>
       <c r="AJ8">
-        <v>0.1444966092853417</v>
+        <v>-0.1004070556309363</v>
       </c>
       <c r="AK8">
-        <v>0.2623106060606061</v>
+        <v>-0.1666666666666668</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1424,7 +1403,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prime Holding for financial investments (S.A.E) (CASE:PRMH)</t>
+          <t>EFG-Hermes Holding S.A.E (CASE:HRHO)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1433,7 +1412,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.218</v>
+        <v>0.152</v>
+      </c>
+      <c r="E9">
+        <v>-0.102</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1448,28 +1430,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>-2.68</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L9">
-        <v>-0.4701754385964912</v>
+        <v>0.2106628242074928</v>
       </c>
       <c r="M9">
-        <v>0.089</v>
+        <v>16.6</v>
       </c>
       <c r="N9">
-        <v>0.006953124999999999</v>
+        <v>0.01967057708259273</v>
       </c>
       <c r="O9">
-        <v>-0.03320895522388059</v>
+        <v>0.2270861833105335</v>
       </c>
       <c r="P9">
-        <v>0.089</v>
+        <v>16.6</v>
       </c>
       <c r="Q9">
-        <v>0.006953124999999999</v>
+        <v>0.01967057708259273</v>
       </c>
       <c r="R9">
-        <v>-0.03320895522388059</v>
+        <v>0.2270861833105335</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1478,61 +1460,64 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>4.02</v>
+        <v>1266.9</v>
       </c>
       <c r="V9">
-        <v>0.3140625</v>
+        <v>1.5012442232492</v>
       </c>
       <c r="W9">
-        <v>-0.1093877551020408</v>
+        <v>0.07957761811452209</v>
       </c>
       <c r="X9">
-        <v>0.09380396257641382</v>
+        <v>0.1662446257880216</v>
       </c>
       <c r="Y9">
-        <v>-0.2031917176784546</v>
+        <v>-0.08666700767349948</v>
       </c>
       <c r="Z9">
-        <v>1.005291005291006</v>
+        <v>0.2381769510604708</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07520873244841406</v>
+        <v>0.1266189451084423</v>
       </c>
       <c r="AC9">
-        <v>-0.07520873244841406</v>
+        <v>-0.1266189451084423</v>
       </c>
       <c r="AD9">
-        <v>13.8</v>
+        <v>884.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>13.8</v>
+        <v>884.6</v>
       </c>
       <c r="AG9">
-        <v>9.780000000000001</v>
+        <v>-382.3000000000001</v>
       </c>
       <c r="AH9">
-        <v>0.518796992481203</v>
+        <v>0.5117732137691641</v>
       </c>
       <c r="AI9">
-        <v>0.3865546218487395</v>
+        <v>0.4705569445183254</v>
       </c>
       <c r="AJ9">
-        <v>0.4331266607617361</v>
+        <v>-0.8282062391681112</v>
       </c>
       <c r="AK9">
-        <v>0.3087121212121213</v>
+        <v>-0.6236541598694945</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>-1.63</v>
+      </c>
+      <c r="AQ9">
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -1543,7 +1528,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EFG-Hermes Holding S.A.E (CASE:HRHO)</t>
+          <t>Beltone Financial Holding SAE (CASE:BTFH)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1552,13 +1537,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.3720000000000001</v>
-      </c>
-      <c r="E10">
-        <v>1.152</v>
-      </c>
-      <c r="F10">
-        <v>0.14</v>
+        <v>-0.142</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1573,85 +1552,82 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>96.7</v>
+        <v>-16.4</v>
       </c>
       <c r="L10">
-        <v>0.2590409858023038</v>
+        <v>-1.378151260504201</v>
       </c>
       <c r="M10">
-        <v>6.58</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.007567567567567567</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.06804550155118924</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>6.58</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.007567567567567567</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.06804550155118924</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>673.6</v>
+        <v>153.9</v>
       </c>
       <c r="V10">
-        <v>0.7746981023576769</v>
+        <v>2.860594795539034</v>
       </c>
       <c r="W10">
-        <v>0.1149001901140684</v>
+        <v>-0.4699140401146132</v>
       </c>
       <c r="X10">
-        <v>0.1064566702396279</v>
+        <v>0.1686811078402887</v>
       </c>
       <c r="Y10">
-        <v>0.008443519874440517</v>
+        <v>-0.6385951479549019</v>
       </c>
       <c r="Z10">
-        <v>0.4080227347251065</v>
+        <v>0.2422145328719723</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07556026998771445</v>
+        <v>0.1300918136455278</v>
       </c>
       <c r="AC10">
-        <v>-0.07556026998771445</v>
+        <v>-0.1300918136455278</v>
       </c>
       <c r="AD10">
-        <v>1268.5</v>
+        <v>58.8</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1268.5</v>
+        <v>58.8</v>
       </c>
       <c r="AG10">
-        <v>594.9</v>
+        <v>-95.10000000000001</v>
       </c>
       <c r="AH10">
-        <v>0.593311506080449</v>
+        <v>0.522202486678508</v>
       </c>
       <c r="AI10">
-        <v>0.5736444625333513</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="AJ10">
-        <v>0.4062414640808522</v>
+        <v>2.302663438256658</v>
       </c>
       <c r="AK10">
-        <v>0.3868765038694154</v>
+        <v>1.161172161172161</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1668,7 +1644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Beltone Financial Holding SAE (CASE:BTFH)</t>
+          <t>Pioneers Holding Company For Financial Investments (S.A.E.) (CASE:ASPI)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1677,7 +1653,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.197</v>
+        <v>-0.583</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1692,88 +1668,94 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>-5.47</v>
+        <v>-4.58</v>
       </c>
       <c r="L11">
-        <v>-0.2863874345549738</v>
+        <v>-1.013274336283186</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>0.255</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.02073170731707317</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>-0.0556768558951965</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>0.255</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.02073170731707317</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>-0.0556768558951965</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
       <c r="U11">
-        <v>47.9</v>
+        <v>13.7</v>
       </c>
       <c r="V11">
-        <v>1.088636363636364</v>
+        <v>1.113821138211382</v>
       </c>
       <c r="W11">
-        <v>-0.1406169665809769</v>
+        <v>-0.009265628161035808</v>
       </c>
       <c r="X11">
-        <v>0.1086537036320104</v>
+        <v>0.1609579037052311</v>
       </c>
       <c r="Y11">
-        <v>-0.2492706702129873</v>
+        <v>-0.1702235318662669</v>
       </c>
       <c r="Z11">
-        <v>0.465740063399171</v>
+        <v>0.006751306945481702</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07803730786052698</v>
+        <v>0.1301337751328759</v>
       </c>
       <c r="AC11">
-        <v>-0.07803730786052698</v>
+        <v>-0.1301337751328759</v>
       </c>
       <c r="AD11">
-        <v>67.09999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>67.09999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="AG11">
-        <v>19.2</v>
+        <v>-2</v>
       </c>
       <c r="AH11">
-        <v>0.6039603960396039</v>
+        <v>0.4875</v>
       </c>
       <c r="AI11">
-        <v>0.657843137254902</v>
+        <v>0.5176991150442477</v>
       </c>
       <c r="AJ11">
-        <v>0.3037974683544303</v>
+        <v>-0.1941747572815534</v>
       </c>
       <c r="AK11">
-        <v>0.354898336414048</v>
+        <v>-0.2247191011235955</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>-0.268</v>
+      </c>
+      <c r="AQ11">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/egypt/egypt_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.03015</v>
+        <v>0.0203</v>
       </c>
       <c r="E2">
-        <v>-0.0397</v>
+        <v>0.1665</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.04320190528257188</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.04320190528257188</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.04980001445300104</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.04073303396204986</v>
       </c>
       <c r="K2">
-        <v>51.877</v>
+        <v>88.599</v>
       </c>
       <c r="L2">
-        <v>0.1409609155924613</v>
+        <v>0.1391871129502031</v>
       </c>
       <c r="M2">
-        <v>17.393</v>
+        <v>16.852</v>
       </c>
       <c r="N2">
-        <v>0.01861984282381858</v>
+        <v>0.01888179271708684</v>
       </c>
       <c r="O2">
-        <v>0.3352738207683559</v>
+        <v>0.1902053070576417</v>
       </c>
       <c r="P2">
-        <v>17.393</v>
+        <v>16.852</v>
       </c>
       <c r="Q2">
-        <v>0.01861984282381858</v>
+        <v>0.01888179271708684</v>
       </c>
       <c r="R2">
-        <v>0.3352738207683559</v>
+        <v>0.1902053070576417</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,64 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1439.072</v>
+        <v>1428.108</v>
       </c>
       <c r="V2">
-        <v>1.540579224524709</v>
+        <v>1.600121008403361</v>
       </c>
       <c r="W2">
-        <v>-0.02491349480968858</v>
+        <v>0.0859752240207296</v>
       </c>
       <c r="X2">
-        <v>0.1125791895416486</v>
+        <v>0.1353870501001095</v>
       </c>
       <c r="Y2">
-        <v>-0.1374926843513371</v>
+        <v>-0.04941182607937988</v>
       </c>
       <c r="Z2">
-        <v>0.168201404390136</v>
+        <v>1.644498754766506</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1115167855104068</v>
+        <v>0.1210966789165276</v>
       </c>
       <c r="AC2">
-        <v>-0.1115167855104068</v>
+        <v>-0.111143786011369</v>
       </c>
       <c r="AD2">
-        <v>956.003</v>
+        <v>933.635</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>956.003</v>
+        <v>933.635</v>
       </c>
       <c r="AG2">
-        <v>-483.0690000000001</v>
+        <v>-494.473</v>
       </c>
       <c r="AH2">
-        <v>0.5057911850819581</v>
+        <v>0.5112628584414625</v>
       </c>
       <c r="AI2">
-        <v>0.4802895996527456</v>
+        <v>0.435788284661397</v>
       </c>
       <c r="AJ2">
-        <v>-1.071006691172884</v>
+        <v>-1.24231019503702</v>
       </c>
       <c r="AK2">
-        <v>-0.8760772578890099</v>
+        <v>-0.6922512624300535</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>29.5</v>
       </c>
       <c r="AM2">
-        <v>-2.202</v>
+        <v>25.445</v>
+      </c>
+      <c r="AN2">
+        <v>28.2919696969697</v>
+      </c>
+      <c r="AO2">
+        <v>1.074576271186441</v>
+      </c>
+      <c r="AP2">
+        <v>-14.9840303030303</v>
       </c>
       <c r="AQ2">
-        <v>-0</v>
+        <v>1.24582432697976</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Osool ESB Securities Brokerage (CASE:EBSC)</t>
+          <t>Pioneers Properties for Urban Development (CASE:PRDC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,110 +721,101 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.0471</v>
-      </c>
-      <c r="E3">
-        <v>0.0322</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1277881040892193</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1277881040892193</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.1473048327137547</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.118848217303143</v>
       </c>
       <c r="K3">
-        <v>0.147</v>
+        <v>5.8</v>
       </c>
       <c r="L3">
-        <v>0.1906614785992218</v>
+        <v>0.02695167286245353</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.43</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01864406779661017</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.246551724137931</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.43</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01864406779661017</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.246551724137931</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>2.71</v>
+        <v>51.2</v>
       </c>
       <c r="V3">
-        <v>0.4927272727272727</v>
-      </c>
-      <c r="W3">
-        <v>0.04468085106382978</v>
+        <v>0.6675358539765319</v>
       </c>
       <c r="X3">
-        <v>0.1091190460079253</v>
-      </c>
-      <c r="Y3">
-        <v>-0.06443819494409547</v>
-      </c>
-      <c r="Z3">
-        <v>0.2930444697833524</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
+        <v>0.2836928329302227</v>
       </c>
       <c r="AB3">
-        <v>0.1091190460079253</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1091190460079253</v>
+        <v>0.139260995460972</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>303.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>303.2</v>
       </c>
       <c r="AG3">
-        <v>-2.71</v>
+        <v>252</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.7981047644116873</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.4777812795461709</v>
       </c>
       <c r="AJ3">
-        <v>-0.9713261648745519</v>
+        <v>0.7666565257073319</v>
       </c>
       <c r="AK3">
-        <v>-15.05555555555554</v>
+        <v>0.4319506342132328</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>29.5</v>
       </c>
       <c r="AM3">
-        <v>-0.116</v>
+        <v>25.9</v>
+      </c>
+      <c r="AN3">
+        <v>9.187878787878788</v>
+      </c>
+      <c r="AO3">
+        <v>1.074576271186441</v>
+      </c>
+      <c r="AP3">
+        <v>7.636363636363637</v>
       </c>
       <c r="AQ3">
-        <v>-0</v>
+        <v>1.223938223938224</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alexandria National Company For Financial Investment SAE (CASE:ANFI)</t>
+          <t>Egyptian Arabian Company (Themar) for securities Brokerage EAC (CASE:EASB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -834,86 +834,110 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.0182</v>
+      </c>
+      <c r="E4">
+        <v>0.158</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
       <c r="K4">
-        <v>-0.391</v>
+        <v>0.624</v>
+      </c>
+      <c r="L4">
+        <v>0.6812227074235807</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.453</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02136792452830189</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.7259615384615384</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.453</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02136792452830189</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.7259615384615384</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0.008</v>
+        <v>1.8</v>
       </c>
       <c r="V4">
-        <v>0.004232804232804233</v>
+        <v>0.0849056603773585</v>
       </c>
       <c r="W4">
-        <v>-0.3969543147208122</v>
+        <v>0.1503614457831325</v>
       </c>
       <c r="X4">
-        <v>0.1091190460079253</v>
+        <v>0.1008160721543013</v>
       </c>
       <c r="Y4">
-        <v>-0.5060733607287374</v>
+        <v>0.04954537362883117</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>0.2568704430734716</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1091190460079253</v>
+        <v>0.1009598088940601</v>
       </c>
       <c r="AC4">
-        <v>-0.1091190460079253</v>
+        <v>-0.1009598088940601</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.795</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.795</v>
       </c>
       <c r="AG4">
-        <v>-0.008</v>
+        <v>-1.005</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.03614457831325301</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.2211404728789986</v>
       </c>
       <c r="AJ4">
-        <v>-0.004250797024442084</v>
+        <v>-0.04976479326565981</v>
       </c>
       <c r="AK4">
-        <v>-0.01891252955082742</v>
+        <v>-0.5598885793871866</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.015</v>
+        <v>-0.013</v>
       </c>
       <c r="AQ4">
         <v>-0</v>
@@ -927,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>El Kahera El Watania Investment (CASE:KWIN)</t>
+          <t>Osool ESB Securities Brokerage (CASE:EBSC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -936,7 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.112</v>
+        <v>0.0203</v>
+      </c>
+      <c r="E5">
+        <v>0.175</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -951,10 +978,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-0.239</v>
+        <v>0.165</v>
       </c>
       <c r="L5">
-        <v>-0.2918192918192918</v>
+        <v>0.2578125</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -963,7 +990,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -972,67 +999,67 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.055</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="V5">
-        <v>0.01264367816091954</v>
+        <v>0.1866050808314088</v>
       </c>
       <c r="W5">
-        <v>-0.03494152046783626</v>
+        <v>0.05709342560553633</v>
       </c>
       <c r="X5">
-        <v>0.1093194957022927</v>
+        <v>0.10122191025673</v>
       </c>
       <c r="Y5">
-        <v>-0.1442610161701289</v>
+        <v>-0.04412848465119362</v>
       </c>
       <c r="Z5">
-        <v>0.1329329654276903</v>
+        <v>3.555555555555553</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1092770199398229</v>
+        <v>0.1013795649306474</v>
       </c>
       <c r="AC5">
-        <v>-0.1092770199398229</v>
+        <v>-0.1013795649306474</v>
       </c>
       <c r="AD5">
-        <v>0.016</v>
+        <v>0.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.016</v>
+        <v>0.2</v>
       </c>
       <c r="AG5">
-        <v>-0.039</v>
+        <v>-0.6080000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.003664681630783326</v>
+        <v>0.04415011037527594</v>
       </c>
       <c r="AI5">
-        <v>0.003061615001913509</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AJ5">
-        <v>-0.009046624913013222</v>
+        <v>-0.1633530360021494</v>
       </c>
       <c r="AK5">
-        <v>-0.007542061496809128</v>
+        <v>-0.4367816091954024</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.005</v>
+        <v>-0.063</v>
       </c>
       <c r="AQ5">
         <v>-0</v>
@@ -1046,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Grand Capital for Financial Investments (CASE:GRCA)</t>
+          <t>Prime Holding S.A.E (CASE:PRMH)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1055,7 +1082,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.195</v>
+        <v>0.0429</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1070,91 +1097,91 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>-0.07199999999999999</v>
+        <v>-0.507</v>
       </c>
       <c r="L6">
-        <v>-0.05106382978723404</v>
+        <v>-0.1258064516129032</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>0.036</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.004152249134948096</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-0.0710059171597633</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>0.036</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.004152249134948096</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>-0.0710059171597633</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>0.32</v>
+        <v>13.4</v>
       </c>
       <c r="V6">
-        <v>0.1167883211678832</v>
+        <v>1.545559400230681</v>
       </c>
       <c r="W6">
-        <v>-0.02491349480968858</v>
+        <v>-0.0325</v>
       </c>
       <c r="X6">
-        <v>0.1115455663729068</v>
+        <v>0.1348341575705569</v>
       </c>
       <c r="Y6">
-        <v>-0.1364590611825953</v>
+        <v>-0.1673341575705569</v>
       </c>
       <c r="Z6">
-        <v>0.6688804554079696</v>
+        <v>0.4099694811800612</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1109565969070591</v>
+        <v>0.1209080070920905</v>
       </c>
       <c r="AC6">
-        <v>-0.1109565969070591</v>
+        <v>-0.1209080070920905</v>
       </c>
       <c r="AD6">
-        <v>0.122</v>
+        <v>6.64</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.122</v>
+        <v>6.64</v>
       </c>
       <c r="AG6">
-        <v>-0.198</v>
+        <v>-6.760000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.04262753319357093</v>
+        <v>0.4337034617896799</v>
       </c>
       <c r="AI6">
-        <v>0.05121746431570109</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="AJ6">
-        <v>-0.07789142407553107</v>
+        <v>-3.539267015706808</v>
       </c>
       <c r="AK6">
-        <v>-0.09602327837051408</v>
+        <v>-2.852320675105485</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-0.168</v>
-      </c>
-      <c r="AQ6">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1165,7 +1192,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Egyptian Arabian Company (Themar) for securities Brokerage EAC (CASE:EASB)</t>
+          <t>EFG Holding (CASE:HRHO)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1174,10 +1201,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0132</v>
+        <v>0.28</v>
       </c>
       <c r="E7">
-        <v>-0.0397</v>
+        <v>0.216</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1192,28 +1219,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0.437</v>
+        <v>81.7</v>
       </c>
       <c r="L7">
-        <v>0.3143884892086331</v>
+        <v>0.1998043531425777</v>
       </c>
       <c r="M7">
-        <v>0.538</v>
+        <v>14.9</v>
       </c>
       <c r="N7">
-        <v>0.06099773242630386</v>
+        <v>0.01934562451311348</v>
       </c>
       <c r="O7">
-        <v>1.231121281464531</v>
+        <v>0.182374541003672</v>
       </c>
       <c r="P7">
-        <v>0.538</v>
+        <v>14.9</v>
       </c>
       <c r="Q7">
-        <v>0.06099773242630386</v>
+        <v>0.01934562451311348</v>
       </c>
       <c r="R7">
-        <v>1.231121281464531</v>
+        <v>0.182374541003672</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1222,55 +1249,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1.2</v>
+        <v>1348.1</v>
       </c>
       <c r="V7">
-        <v>0.1360544217687075</v>
+        <v>1.75032459101532</v>
       </c>
       <c r="W7">
-        <v>0.1021028037383177</v>
+        <v>0.09699631960109226</v>
       </c>
       <c r="X7">
-        <v>0.1125791895416486</v>
+        <v>0.135939942629662</v>
       </c>
       <c r="Y7">
-        <v>-0.01047638580333081</v>
+        <v>-0.03894362302856977</v>
       </c>
       <c r="Z7">
-        <v>2.168486739469579</v>
+        <v>1.121503017004937</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1115167855104068</v>
+        <v>0.1212853507409648</v>
       </c>
       <c r="AC7">
-        <v>-0.1115167855104068</v>
+        <v>-0.1212853507409648</v>
       </c>
       <c r="AD7">
-        <v>0.5600000000000001</v>
+        <v>608.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.5600000000000001</v>
+        <v>608.1</v>
       </c>
       <c r="AG7">
-        <v>-0.6399999999999999</v>
+        <v>-739.9999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.05970149253731343</v>
+        <v>0.4411956758325473</v>
       </c>
       <c r="AI7">
-        <v>0.1296296296296296</v>
+        <v>0.4156527682843473</v>
       </c>
       <c r="AJ7">
-        <v>-0.07823960880195598</v>
+        <v>-24.50331125827801</v>
       </c>
       <c r="AK7">
-        <v>-0.2051282051282051</v>
+        <v>-6.440382941688418</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1287,7 +1314,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>El Orouba Securities Brokerage (CASE:EOSB)</t>
+          <t>Pioneers Holding Company For Financial Investments (S.A.E.) (CASE:ASPI)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1296,7 +1323,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.183</v>
+        <v>-0.499</v>
+      </c>
+      <c r="E8">
+        <v>-0.498</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1311,450 +1341,93 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>-0.125</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="L8">
-        <v>-0.5841121495327103</v>
+        <v>0.1190962099125364</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>0.033</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.002894736842105263</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>0.04039167686658507</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>0.033</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.002894736842105263</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>0.04039167686658507</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>0.279</v>
+        <v>12.8</v>
       </c>
       <c r="V8">
-        <v>0.344019728729963</v>
+        <v>1.12280701754386</v>
       </c>
       <c r="W8">
-        <v>-0.1623376623376623</v>
+        <v>0.07495412844036696</v>
       </c>
       <c r="X8">
-        <v>0.122894555791537</v>
+        <v>0.159289614830132</v>
       </c>
       <c r="Y8">
-        <v>-0.2852322181291994</v>
+        <v>-0.08433548638976505</v>
       </c>
       <c r="Z8">
-        <v>0.2491268917345751</v>
+        <v>0.7707865168539324</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.1172226267329705</v>
+        <v>0.127430996907725</v>
       </c>
       <c r="AC8">
-        <v>-0.1172226267329705</v>
+        <v>-0.127430996907725</v>
       </c>
       <c r="AD8">
-        <v>0.205</v>
+        <v>14.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.205</v>
+        <v>14.7</v>
       </c>
       <c r="AG8">
-        <v>-0.07400000000000004</v>
+        <v>1.899999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.2017716535433071</v>
+        <v>0.5632183908045977</v>
       </c>
       <c r="AI8">
-        <v>0.2835408022130014</v>
+        <v>0.6325301204819277</v>
       </c>
       <c r="AJ8">
-        <v>-0.1004070556309363</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AK8">
-        <v>-0.1666666666666668</v>
+        <v>0.1819923371647509</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>EFG-Hermes Holding S.A.E (CASE:HRHO)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>0.152</v>
-      </c>
-      <c r="E9">
-        <v>-0.102</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="L9">
-        <v>0.2106628242074928</v>
-      </c>
-      <c r="M9">
-        <v>16.6</v>
-      </c>
-      <c r="N9">
-        <v>0.01967057708259273</v>
-      </c>
-      <c r="O9">
-        <v>0.2270861833105335</v>
-      </c>
-      <c r="P9">
-        <v>16.6</v>
-      </c>
-      <c r="Q9">
-        <v>0.01967057708259273</v>
-      </c>
-      <c r="R9">
-        <v>0.2270861833105335</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>1266.9</v>
-      </c>
-      <c r="V9">
-        <v>1.5012442232492</v>
-      </c>
-      <c r="W9">
-        <v>0.07957761811452209</v>
-      </c>
-      <c r="X9">
-        <v>0.1662446257880216</v>
-      </c>
-      <c r="Y9">
-        <v>-0.08666700767349948</v>
-      </c>
-      <c r="Z9">
-        <v>0.2381769510604708</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.1266189451084423</v>
-      </c>
-      <c r="AC9">
-        <v>-0.1266189451084423</v>
-      </c>
-      <c r="AD9">
-        <v>884.6</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>884.6</v>
-      </c>
-      <c r="AG9">
-        <v>-382.3000000000001</v>
-      </c>
-      <c r="AH9">
-        <v>0.5117732137691641</v>
-      </c>
-      <c r="AI9">
-        <v>0.4705569445183254</v>
-      </c>
-      <c r="AJ9">
-        <v>-0.8282062391681112</v>
-      </c>
-      <c r="AK9">
-        <v>-0.6236541598694945</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>-1.63</v>
-      </c>
-      <c r="AQ9">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Beltone Financial Holding SAE (CASE:BTFH)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>-0.142</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>-16.4</v>
-      </c>
-      <c r="L10">
-        <v>-1.378151260504201</v>
-      </c>
-      <c r="M10">
-        <v>-0</v>
-      </c>
-      <c r="N10">
-        <v>-0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>-0</v>
-      </c>
-      <c r="Q10">
-        <v>-0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>153.9</v>
-      </c>
-      <c r="V10">
-        <v>2.860594795539034</v>
-      </c>
-      <c r="W10">
-        <v>-0.4699140401146132</v>
-      </c>
-      <c r="X10">
-        <v>0.1686811078402887</v>
-      </c>
-      <c r="Y10">
-        <v>-0.6385951479549019</v>
-      </c>
-      <c r="Z10">
-        <v>0.2422145328719723</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0.1300918136455278</v>
-      </c>
-      <c r="AC10">
-        <v>-0.1300918136455278</v>
-      </c>
-      <c r="AD10">
-        <v>58.8</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>58.8</v>
-      </c>
-      <c r="AG10">
-        <v>-95.10000000000001</v>
-      </c>
-      <c r="AH10">
-        <v>0.522202486678508</v>
-      </c>
-      <c r="AI10">
-        <v>0.8166666666666667</v>
-      </c>
-      <c r="AJ10">
-        <v>2.302663438256658</v>
-      </c>
-      <c r="AK10">
-        <v>1.161172161172161</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pioneers Holding Company For Financial Investments (S.A.E.) (CASE:ASPI)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>-0.583</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>-4.58</v>
-      </c>
-      <c r="L11">
-        <v>-1.013274336283186</v>
-      </c>
-      <c r="M11">
-        <v>0.255</v>
-      </c>
-      <c r="N11">
-        <v>0.02073170731707317</v>
-      </c>
-      <c r="O11">
-        <v>-0.0556768558951965</v>
-      </c>
-      <c r="P11">
-        <v>0.255</v>
-      </c>
-      <c r="Q11">
-        <v>0.02073170731707317</v>
-      </c>
-      <c r="R11">
-        <v>-0.0556768558951965</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>13.7</v>
-      </c>
-      <c r="V11">
-        <v>1.113821138211382</v>
-      </c>
-      <c r="W11">
-        <v>-0.009265628161035808</v>
-      </c>
-      <c r="X11">
-        <v>0.1609579037052311</v>
-      </c>
-      <c r="Y11">
-        <v>-0.1702235318662669</v>
-      </c>
-      <c r="Z11">
-        <v>0.006751306945481702</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.1301337751328759</v>
-      </c>
-      <c r="AC11">
-        <v>-0.1301337751328759</v>
-      </c>
-      <c r="AD11">
-        <v>11.7</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>11.7</v>
-      </c>
-      <c r="AG11">
-        <v>-2</v>
-      </c>
-      <c r="AH11">
-        <v>0.4875</v>
-      </c>
-      <c r="AI11">
-        <v>0.5176991150442477</v>
-      </c>
-      <c r="AJ11">
-        <v>-0.1941747572815534</v>
-      </c>
-      <c r="AK11">
-        <v>-0.2247191011235955</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>-0.268</v>
-      </c>
-      <c r="AQ11">
+        <v>-0.379</v>
+      </c>
+      <c r="AQ8">
         <v>-0</v>
       </c>
     </row>
